--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260904.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.53%</t>
+          <t>26.37%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.29%</t>
+          <t>8.48%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.97%</t>
+          <t>7.91%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>6.08%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>4.50%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>65,245</t>
+          <t>19,695</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,695</t>
+          <t>65,245</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>109,936,178</t>
+          <t>50,845</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>50,845</t>
+          <t>19,490</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>19,490</t>
+          <t>36,050</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,050</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1034,24 +1034,24 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1078,90 +1078,90 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,990</t>
+          <t>18,355</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>18,355</t>
+          <t>125,985</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>125,985</t>
+          <t>19,587</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,871</t>
+          <t>53,750,456</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>19,587</t>
+          <t>15,871</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1210,24 +1210,24 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>37,340</t>
+          <t>42,930</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,930</t>
+          <t>37,340</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1293,34 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>375,446</t>
+          <t>386,617</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>5,414</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
